--- a/docs/data-penduduk-contoh.xlsx
+++ b/docs/data-penduduk-contoh.xlsx
@@ -491,12 +491,12 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Kode Keluarga</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>Kode Warga</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Kode Keluarga</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -603,12 +603,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>K0001</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
           <t>W0001-1</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>K0001</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>K0001</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>W0001-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>K0001</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -827,12 +827,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>K0001</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
           <t>W0001-3</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>K0001</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -939,12 +939,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>K0001</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
           <t>W0001-4</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>K0001</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1051,12 +1051,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>K0001</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
           <t>W0001-5</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>K0001</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1163,12 +1163,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>K0002</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
           <t>W0002-1</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>K0002</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1275,12 +1275,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>K0002</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
           <t>W0002-2</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>K0002</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1387,12 +1387,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>K0002</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
           <t>W0002-3</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>K0002</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1499,12 +1499,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>K0002</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
           <t>W0002-4</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>K0002</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1611,12 +1611,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>K0003</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
           <t>W0003-1</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>K0003</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1723,12 +1723,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>K0003</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>W0003-2</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>K0003</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>K0003</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
           <t>W0003-3</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>K0003</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1947,12 +1947,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>K0003</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
           <t>W0003-4</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>K0003</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -2059,14 +2059,14 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>K0003</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>W0003-5</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>K0003</t>
-        </is>
-      </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Widya Prasetyo</t>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -2171,12 +2171,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>K0004</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
           <t>W0004-1</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>K0004</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2283,12 +2283,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>K0004</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
           <t>W0004-2</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>K0004</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -2395,12 +2395,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>K0004</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>W0004-3</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>K0004</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -2507,12 +2507,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>K0005</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
           <t>W0005-1</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>K0005</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -2619,12 +2619,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
+          <t>K0005</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>W0005-2</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>K0005</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2731,12 +2731,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t>K0005</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
           <t>W0005-3</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>K0005</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2843,12 +2843,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>K0006</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
           <t>W0006-1</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>K0006</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2955,12 +2955,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t>K0006</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
           <t>W0006-2</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>K0006</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -3067,12 +3067,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
+          <t>K0006</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
           <t>W0006-3</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>K0006</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -3179,12 +3179,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>K0006</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
           <t>W0006-4</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>K0006</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -3291,14 +3291,14 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
+          <t>K0006</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
           <t>W0006-5</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>K0006</t>
-        </is>
-      </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Keisha Ramadhan</t>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -3403,12 +3403,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
+          <t>K0007</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
           <t>W0007-1</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>K0007</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3515,12 +3515,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
+          <t>K0007</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
           <t>W0007-2</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>K0007</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -3627,12 +3627,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t>K0007</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
           <t>W0007-3</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>K0007</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -3739,12 +3739,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
+          <t>K0007</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
           <t>W0007-4</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>K0007</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -3851,12 +3851,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
+          <t>K0008</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
           <t>W0008-1</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>K0008</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -3963,12 +3963,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
+          <t>K0008</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
           <t>W0008-2</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>K0008</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -4075,12 +4075,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t>K0008</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
           <t>W0008-3</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>K0008</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -4187,12 +4187,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
+          <t>K0009</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
           <t>W0009-1</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>K0009</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -4299,12 +4299,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
+          <t>K0009</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
           <t>W0009-2</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>K0009</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -4411,12 +4411,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
+          <t>K0009</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
           <t>W0009-3</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>K0009</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -4523,12 +4523,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
+          <t>K0010</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
           <t>W0010-1</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>K0010</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -4635,12 +4635,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
+          <t>K0010</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
           <t>W0010-2</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>K0010</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -4747,12 +4747,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
+          <t>K0010</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
           <t>W0010-3</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>K0010</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -4859,12 +4859,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
+          <t>K0011</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
           <t>W0011-1</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>K0011</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -4971,12 +4971,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
+          <t>K0011</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
           <t>W0011-2</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>K0011</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
+          <t>K0011</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
           <t>W0011-3</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>K0011</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -5195,12 +5195,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
+          <t>K0011</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
           <t>W0011-4</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>K0011</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -5307,12 +5307,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
+          <t>K0011</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
           <t>W0011-5</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>K0011</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -5419,12 +5419,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
+          <t>K0012</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
           <t>W0012-1</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>K0012</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -5531,12 +5531,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
+          <t>K0012</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
           <t>W0012-2</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>K0012</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -5643,12 +5643,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
+          <t>K0012</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
           <t>W0012-3</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>K0012</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -5755,14 +5755,14 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
+          <t>K0012</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
           <t>W0012-4</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>K0012</t>
-        </is>
-      </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Salma Prasetyo</t>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -5867,14 +5867,14 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
+          <t>K0012</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
           <t>W0012-5</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>K0012</t>
-        </is>
-      </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
           <t>Bayu Prasetyo</t>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -5979,12 +5979,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
+          <t>K0013</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
           <t>W0013-1</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>K0013</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -6091,12 +6091,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
+          <t>K0013</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
           <t>W0013-2</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>K0013</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -6203,12 +6203,12 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
+          <t>K0013</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
           <t>W0013-3</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>K0013</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -6315,12 +6315,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
+          <t>K0013</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
           <t>W0013-4</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>K0013</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -6427,12 +6427,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
+          <t>K0014</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
           <t>W0014-1</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>K0014</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -6539,12 +6539,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
+          <t>K0014</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
           <t>W0014-2</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>K0014</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -6651,12 +6651,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
+          <t>K0014</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
           <t>W0014-3</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>K0014</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -6763,12 +6763,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
+          <t>K0014</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
           <t>W0014-4</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>K0014</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -6875,12 +6875,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
+          <t>K0014</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
           <t>W0014-5</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>K0014</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -6987,12 +6987,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
+          <t>K0015</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
           <t>W0015-1</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>K0015</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -7099,12 +7099,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
+          <t>K0015</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
           <t>W0015-2</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>K0015</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -7211,12 +7211,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
+          <t>K0015</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
           <t>W0015-3</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>K0015</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -7323,12 +7323,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
+          <t>K0015</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
           <t>W0015-4</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>K0015</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -7435,12 +7435,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
+          <t>K0016</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
           <t>W0016-1</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>K0016</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -7547,12 +7547,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
+          <t>K0016</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
           <t>W0016-2</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>K0016</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -7659,14 +7659,14 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
+          <t>K0016</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
           <t>W0016-3</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>K0016</t>
-        </is>
-      </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
           <t>Jefri Santoso</t>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -7771,12 +7771,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
+          <t>K0017</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
           <t>W0017-1</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>K0017</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -7883,12 +7883,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
+          <t>K0017</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
           <t>W0017-2</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>K0017</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -7995,14 +7995,14 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
+          <t>K0017</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
           <t>W0017-3</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>K0017</t>
-        </is>
-      </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
           <t>Kevin Wijaya</t>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -8107,12 +8107,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
+          <t>K0018</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
           <t>W0018-1</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>K0018</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -8219,12 +8219,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
+          <t>K0018</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
           <t>W0018-2</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>K0018</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -8331,14 +8331,14 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
+          <t>K0018</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
           <t>W0018-3</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>K0018</t>
-        </is>
-      </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
           <t>Hana Saputra</t>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -8443,12 +8443,12 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
+          <t>K0018</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
           <t>W0018-4</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>K0018</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -8555,12 +8555,12 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
+          <t>K0018</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
           <t>W0018-5</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>K0018</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -8667,12 +8667,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
+          <t>K0019</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
           <t>W0019-1</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>K0019</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -8779,12 +8779,12 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
+          <t>K0019</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
           <t>W0019-2</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>K0019</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -8891,14 +8891,14 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
+          <t>K0019</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
           <t>W0019-3</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>K0019</t>
-        </is>
-      </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
           <t>Jefri Setiawan</t>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
@@ -9003,12 +9003,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
+          <t>K0020</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
           <t>W0020-1</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>K0020</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -9115,12 +9115,12 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
+          <t>K0020</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
           <t>W0020-2</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>K0020</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -9227,12 +9227,12 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
+          <t>K0020</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
           <t>W0020-3</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>K0020</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -9339,12 +9339,12 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
+          <t>K0021</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
           <t>W0021-1</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>K0021</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -9451,12 +9451,12 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
+          <t>K0021</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
           <t>W0021-2</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>K0021</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -9563,12 +9563,12 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
+          <t>K0021</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
           <t>W0021-3</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>K0021</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -9675,12 +9675,12 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
+          <t>K0021</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
           <t>W0021-4</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>K0021</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -9787,12 +9787,12 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
+          <t>K0022</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
           <t>W0022-1</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>K0022</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -9899,12 +9899,12 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
+          <t>K0022</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
           <t>W0022-2</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>K0022</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -10011,12 +10011,12 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
+          <t>K0022</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
           <t>W0022-3</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>K0022</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -10123,12 +10123,12 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
+          <t>K0022</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
           <t>W0022-4</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>K0022</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -10235,14 +10235,14 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
+          <t>K0022</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
           <t>W0022-5</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>K0022</t>
-        </is>
-      </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
           <t>Cahyo Wijaya</t>
@@ -10275,7 +10275,7 @@
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J89" s="3" t="inlineStr">
@@ -10347,12 +10347,12 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
+          <t>K0023</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
           <t>W0023-1</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>K0023</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -10459,12 +10459,12 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
+          <t>K0023</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
           <t>W0023-2</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>K0023</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -10571,14 +10571,14 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
+          <t>K0023</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
           <t>W0023-3</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>K0023</t>
-        </is>
-      </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
           <t>Hafiz Sanjaya</t>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="I92" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J92" s="3" t="inlineStr">
@@ -10683,12 +10683,12 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
+          <t>K0023</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
           <t>W0023-4</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>K0023</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -10795,12 +10795,12 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
+          <t>K0023</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
           <t>W0023-5</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>K0023</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -10907,12 +10907,12 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
+          <t>K0024</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
           <t>W0024-1</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>K0024</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -11019,12 +11019,12 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
+          <t>K0024</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
           <t>W0024-2</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>K0024</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -11131,12 +11131,12 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
+          <t>K0024</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
           <t>W0024-3</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>K0024</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -11243,14 +11243,14 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
+          <t>K0024</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
           <t>W0024-4</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>K0024</t>
-        </is>
-      </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
           <t>Rani Wijaya</t>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="I98" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J98" s="3" t="inlineStr">
@@ -11355,12 +11355,12 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
+          <t>K0024</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
           <t>W0024-5</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>K0024</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -11467,12 +11467,12 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
+          <t>K0025</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
           <t>W0025-1</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>K0025</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -11579,12 +11579,12 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
+          <t>K0025</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
           <t>W0025-2</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>K0025</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -11691,12 +11691,12 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
+          <t>K0025</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
           <t>W0025-3</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>K0025</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -11803,12 +11803,12 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
+          <t>K0025</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
           <t>W0025-4</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>K0025</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -11915,12 +11915,12 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
+          <t>K0025</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
           <t>W0025-5</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>K0025</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -12027,12 +12027,12 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
+          <t>K0026</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
           <t>W0026-1</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>K0026</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -12139,12 +12139,12 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
+          <t>K0026</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
           <t>W0026-2</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>K0026</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -12251,14 +12251,14 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
+          <t>K0026</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
           <t>W0026-3</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>K0026</t>
-        </is>
-      </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
           <t>Yuni Saputra</t>
@@ -12291,7 +12291,7 @@
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J107" s="3" t="inlineStr">
@@ -12363,12 +12363,12 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
+          <t>K0027</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
           <t>W0027-1</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>K0027</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -12475,12 +12475,12 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
+          <t>K0027</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
           <t>W0027-2</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>K0027</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -12587,12 +12587,12 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
+          <t>K0027</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
           <t>W0027-3</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>K0027</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -12699,12 +12699,12 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
+          <t>K0027</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
           <t>W0027-4</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>K0027</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -12811,12 +12811,12 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
+          <t>K0027</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
           <t>W0027-5</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>K0027</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -12923,12 +12923,12 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
+          <t>K0028</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
           <t>W0028-1</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>K0028</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -13035,12 +13035,12 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
+          <t>K0028</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
           <t>W0028-2</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>K0028</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -13147,12 +13147,12 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
+          <t>K0028</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
           <t>W0028-3</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>K0028</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -13259,12 +13259,12 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
+          <t>K0028</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
           <t>W0028-4</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>K0028</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -13371,12 +13371,12 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
+          <t>K0029</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
           <t>W0029-1</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>K0029</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -13483,12 +13483,12 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
+          <t>K0029</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
           <t>W0029-2</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>K0029</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -13595,14 +13595,14 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
+          <t>K0029</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
           <t>W0029-3</t>
         </is>
       </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>K0029</t>
-        </is>
-      </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
           <t>Dara Susanto</t>
@@ -13635,7 +13635,7 @@
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J119" s="3" t="inlineStr">
@@ -13707,12 +13707,12 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
+          <t>K0030</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
           <t>W0030-1</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>K0030</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -13819,12 +13819,12 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
+          <t>K0030</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
           <t>W0030-2</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>K0030</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -13931,12 +13931,12 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
+          <t>K0030</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
           <t>W0030-3</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>K0030</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -14043,12 +14043,12 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
+          <t>K0031</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
           <t>W0031-1</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>K0031</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -14155,12 +14155,12 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
+          <t>K0031</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
           <t>W0031-2</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>K0031</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -14267,12 +14267,12 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
+          <t>K0031</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
           <t>W0031-3</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>K0031</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -14379,12 +14379,12 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
+          <t>K0032</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
           <t>W0032-1</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>K0032</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -14491,12 +14491,12 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
+          <t>K0032</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
           <t>W0032-2</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>K0032</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -14603,12 +14603,12 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
+          <t>K0032</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
           <t>W0032-3</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>K0032</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -14715,12 +14715,12 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
+          <t>K0033</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
           <t>W0033-1</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>K0033</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -14827,12 +14827,12 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
+          <t>K0033</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
           <t>W0033-2</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>K0033</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -14939,14 +14939,14 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
+          <t>K0033</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
           <t>W0033-3</t>
         </is>
       </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>K0033</t>
-        </is>
-      </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
           <t>Yoga Herlambang</t>
@@ -14979,7 +14979,7 @@
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J131" s="3" t="inlineStr">
@@ -15051,12 +15051,12 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
+          <t>K0033</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
           <t>W0033-4</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>K0033</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -15163,12 +15163,12 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
+          <t>K0034</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
           <t>W0034-1</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>K0034</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -15275,12 +15275,12 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
+          <t>K0034</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
           <t>W0034-2</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>K0034</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -15387,12 +15387,12 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
+          <t>K0034</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
           <t>W0034-3</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>K0034</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -15499,12 +15499,12 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
+          <t>K0035</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
           <t>W0035-1</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>K0035</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -15611,12 +15611,12 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
+          <t>K0035</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
           <t>W0035-2</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>K0035</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -15723,12 +15723,12 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
+          <t>K0035</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
           <t>W0035-3</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>K0035</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -15835,12 +15835,12 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
+          <t>K0035</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
           <t>W0035-4</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>K0035</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -15947,12 +15947,12 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
+          <t>K0036</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
           <t>W0036-1</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>K0036</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -16059,12 +16059,12 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
+          <t>K0036</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
           <t>W0036-2</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>K0036</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -16171,14 +16171,14 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
+          <t>K0036</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
           <t>W0036-3</t>
         </is>
       </c>
-      <c r="B142" s="3" t="inlineStr">
-        <is>
-          <t>K0036</t>
-        </is>
-      </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
           <t>Wisnu Permana</t>
@@ -16211,7 +16211,7 @@
       </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J142" s="3" t="inlineStr">
@@ -16283,12 +16283,12 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
+          <t>K0037</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
           <t>W0037-1</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>K0037</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -16395,12 +16395,12 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
+          <t>K0037</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
           <t>W0037-2</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="inlineStr">
-        <is>
-          <t>K0037</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -16507,12 +16507,12 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
+          <t>K0037</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
           <t>W0037-3</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>K0037</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -16619,14 +16619,14 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
+          <t>K0037</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
           <t>W0037-4</t>
         </is>
       </c>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>K0037</t>
-        </is>
-      </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
           <t>Galih Saputra</t>
@@ -16659,7 +16659,7 @@
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J146" s="3" t="inlineStr">
@@ -16731,12 +16731,12 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
+          <t>K0038</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
           <t>W0038-1</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>K0038</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -16843,12 +16843,12 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
+          <t>K0038</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
           <t>W0038-2</t>
-        </is>
-      </c>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>K0038</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -16955,14 +16955,14 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
+          <t>K0038</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
           <t>W0038-3</t>
         </is>
       </c>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>K0038</t>
-        </is>
-      </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
           <t>Salma Wijaya</t>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J149" s="3" t="inlineStr">
@@ -17067,12 +17067,12 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
+          <t>K0038</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
           <t>W0038-4</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t>K0038</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -17179,12 +17179,12 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
+          <t>K0039</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
           <t>W0039-1</t>
-        </is>
-      </c>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>K0039</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -17291,12 +17291,12 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
+          <t>K0039</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
           <t>W0039-2</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t>K0039</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -17403,14 +17403,14 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
+          <t>K0039</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
           <t>W0039-3</t>
         </is>
       </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>K0039</t>
-        </is>
-      </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
           <t>Bunga Wibowo</t>
@@ -17443,7 +17443,7 @@
       </c>
       <c r="I153" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J153" s="3" t="inlineStr">
@@ -17515,12 +17515,12 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
+          <t>K0039</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
           <t>W0039-4</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>K0039</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -17627,12 +17627,12 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
+          <t>K0040</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
           <t>W0040-1</t>
-        </is>
-      </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>K0040</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -17739,12 +17739,12 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
+          <t>K0040</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
           <t>W0040-2</t>
-        </is>
-      </c>
-      <c r="B156" s="3" t="inlineStr">
-        <is>
-          <t>K0040</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -17851,12 +17851,12 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
+          <t>K0040</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
           <t>W0040-3</t>
-        </is>
-      </c>
-      <c r="B157" s="3" t="inlineStr">
-        <is>
-          <t>K0040</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -17963,12 +17963,12 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
+          <t>K0041</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
           <t>W0041-1</t>
-        </is>
-      </c>
-      <c r="B158" s="3" t="inlineStr">
-        <is>
-          <t>K0041</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -18075,12 +18075,12 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
+          <t>K0041</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
           <t>W0041-2</t>
-        </is>
-      </c>
-      <c r="B159" s="3" t="inlineStr">
-        <is>
-          <t>K0041</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -18187,14 +18187,14 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
+          <t>K0041</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
           <t>W0041-3</t>
         </is>
       </c>
-      <c r="B160" s="3" t="inlineStr">
-        <is>
-          <t>K0041</t>
-        </is>
-      </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
           <t>Satria Permana</t>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J160" s="3" t="inlineStr">
@@ -18299,12 +18299,12 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
+          <t>K0042</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
           <t>W0042-1</t>
-        </is>
-      </c>
-      <c r="B161" s="3" t="inlineStr">
-        <is>
-          <t>K0042</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -18411,12 +18411,12 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
+          <t>K0042</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
           <t>W0042-2</t>
-        </is>
-      </c>
-      <c r="B162" s="3" t="inlineStr">
-        <is>
-          <t>K0042</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -18523,12 +18523,12 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
+          <t>K0042</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
           <t>W0042-3</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t>K0042</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -18635,12 +18635,12 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
+          <t>K0043</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
           <t>W0043-1</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t>K0043</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -18747,12 +18747,12 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
+          <t>K0043</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
           <t>W0043-2</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="inlineStr">
-        <is>
-          <t>K0043</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -18859,12 +18859,12 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
+          <t>K0043</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
           <t>W0043-3</t>
-        </is>
-      </c>
-      <c r="B166" s="3" t="inlineStr">
-        <is>
-          <t>K0043</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -18971,12 +18971,12 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
+          <t>K0043</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
           <t>W0043-4</t>
-        </is>
-      </c>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t>K0043</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -19083,12 +19083,12 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
+          <t>K0044</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
           <t>W0044-1</t>
-        </is>
-      </c>
-      <c r="B168" s="3" t="inlineStr">
-        <is>
-          <t>K0044</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -19195,12 +19195,12 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
+          <t>K0044</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
           <t>W0044-2</t>
-        </is>
-      </c>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t>K0044</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -19307,14 +19307,14 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
+          <t>K0044</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
           <t>W0044-3</t>
         </is>
       </c>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t>K0044</t>
-        </is>
-      </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
           <t>Hafiz Kurniawan</t>
@@ -19347,7 +19347,7 @@
       </c>
       <c r="I170" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J170" s="3" t="inlineStr">
@@ -19419,14 +19419,14 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
+          <t>K0044</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
           <t>W0044-4</t>
         </is>
       </c>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t>K0044</t>
-        </is>
-      </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
           <t>Ulfa Kurniawan</t>
@@ -19459,7 +19459,7 @@
       </c>
       <c r="I171" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J171" s="3" t="inlineStr">
@@ -19531,12 +19531,12 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
+          <t>K0045</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
           <t>W0045-1</t>
-        </is>
-      </c>
-      <c r="B172" s="3" t="inlineStr">
-        <is>
-          <t>K0045</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -19643,12 +19643,12 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
+          <t>K0045</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
           <t>W0045-2</t>
-        </is>
-      </c>
-      <c r="B173" s="3" t="inlineStr">
-        <is>
-          <t>K0045</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
@@ -19755,12 +19755,12 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
+          <t>K0045</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
           <t>W0045-3</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>K0045</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -19867,12 +19867,12 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
+          <t>K0045</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
           <t>W0045-4</t>
-        </is>
-      </c>
-      <c r="B175" s="3" t="inlineStr">
-        <is>
-          <t>K0045</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
@@ -19979,12 +19979,12 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
+          <t>K0046</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
           <t>W0046-1</t>
-        </is>
-      </c>
-      <c r="B176" s="3" t="inlineStr">
-        <is>
-          <t>K0046</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -20091,12 +20091,12 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
+          <t>K0046</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
           <t>W0046-2</t>
-        </is>
-      </c>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>K0046</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
@@ -20203,12 +20203,12 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
+          <t>K0046</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
           <t>W0046-3</t>
-        </is>
-      </c>
-      <c r="B178" s="3" t="inlineStr">
-        <is>
-          <t>K0046</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -20315,12 +20315,12 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
+          <t>K0047</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
           <t>W0047-1</t>
-        </is>
-      </c>
-      <c r="B179" s="3" t="inlineStr">
-        <is>
-          <t>K0047</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
@@ -20427,12 +20427,12 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
+          <t>K0047</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
           <t>W0047-2</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t>K0047</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -20539,12 +20539,12 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
+          <t>K0047</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
           <t>W0047-3</t>
-        </is>
-      </c>
-      <c r="B181" s="3" t="inlineStr">
-        <is>
-          <t>K0047</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -20651,12 +20651,12 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
+          <t>K0047</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
           <t>W0047-4</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="inlineStr">
-        <is>
-          <t>K0047</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -20763,12 +20763,12 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
+          <t>K0047</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
           <t>W0047-5</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="inlineStr">
-        <is>
-          <t>K0047</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -20875,12 +20875,12 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
+          <t>K0048</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
           <t>W0048-1</t>
-        </is>
-      </c>
-      <c r="B184" s="3" t="inlineStr">
-        <is>
-          <t>K0048</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -20987,12 +20987,12 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
+          <t>K0048</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
           <t>W0048-2</t>
-        </is>
-      </c>
-      <c r="B185" s="3" t="inlineStr">
-        <is>
-          <t>K0048</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -21099,12 +21099,12 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
+          <t>K0048</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
           <t>W0048-3</t>
-        </is>
-      </c>
-      <c r="B186" s="3" t="inlineStr">
-        <is>
-          <t>K0048</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -21211,12 +21211,12 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
+          <t>K0049</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
           <t>W0049-1</t>
-        </is>
-      </c>
-      <c r="B187" s="3" t="inlineStr">
-        <is>
-          <t>K0049</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -21323,12 +21323,12 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
+          <t>K0049</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
           <t>W0049-2</t>
-        </is>
-      </c>
-      <c r="B188" s="3" t="inlineStr">
-        <is>
-          <t>K0049</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -21435,12 +21435,12 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
+          <t>K0049</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
           <t>W0049-3</t>
-        </is>
-      </c>
-      <c r="B189" s="3" t="inlineStr">
-        <is>
-          <t>K0049</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
@@ -21547,12 +21547,12 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
+          <t>K0049</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
           <t>W0049-4</t>
-        </is>
-      </c>
-      <c r="B190" s="3" t="inlineStr">
-        <is>
-          <t>K0049</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -21659,12 +21659,12 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
+          <t>K0050</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
           <t>W0050-1</t>
-        </is>
-      </c>
-      <c r="B191" s="3" t="inlineStr">
-        <is>
-          <t>K0050</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
@@ -21771,12 +21771,12 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
+          <t>K0050</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
           <t>W0050-2</t>
-        </is>
-      </c>
-      <c r="B192" s="3" t="inlineStr">
-        <is>
-          <t>K0050</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -21883,12 +21883,12 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
+          <t>K0050</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
           <t>W0050-3</t>
-        </is>
-      </c>
-      <c r="B193" s="3" t="inlineStr">
-        <is>
-          <t>K0050</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
@@ -21995,12 +21995,12 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
+          <t>K0050</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
           <t>W0050-4</t>
-        </is>
-      </c>
-      <c r="B194" s="3" t="inlineStr">
-        <is>
-          <t>K0050</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -22107,12 +22107,12 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
+          <t>K0051</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
           <t>W0051-1</t>
-        </is>
-      </c>
-      <c r="B195" s="3" t="inlineStr">
-        <is>
-          <t>K0051</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
@@ -22219,12 +22219,12 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
+          <t>K0051</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
           <t>W0051-2</t>
-        </is>
-      </c>
-      <c r="B196" s="3" t="inlineStr">
-        <is>
-          <t>K0051</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -22331,12 +22331,12 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
+          <t>K0051</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
           <t>W0051-3</t>
-        </is>
-      </c>
-      <c r="B197" s="3" t="inlineStr">
-        <is>
-          <t>K0051</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
@@ -22443,12 +22443,12 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
+          <t>K0051</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
           <t>W0051-4</t>
-        </is>
-      </c>
-      <c r="B198" s="3" t="inlineStr">
-        <is>
-          <t>K0051</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -22555,14 +22555,14 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
+          <t>K0051</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
           <t>W0051-5</t>
         </is>
       </c>
-      <c r="B199" s="3" t="inlineStr">
-        <is>
-          <t>K0051</t>
-        </is>
-      </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
           <t>Wisnu Sanjaya</t>
@@ -22595,7 +22595,7 @@
       </c>
       <c r="I199" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J199" s="3" t="inlineStr">
@@ -22667,12 +22667,12 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
+          <t>K0052</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
           <t>W0052-1</t>
-        </is>
-      </c>
-      <c r="B200" s="3" t="inlineStr">
-        <is>
-          <t>K0052</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
@@ -22779,12 +22779,12 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
+          <t>K0052</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
           <t>W0052-2</t>
-        </is>
-      </c>
-      <c r="B201" s="3" t="inlineStr">
-        <is>
-          <t>K0052</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
@@ -22891,12 +22891,12 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
+          <t>K0052</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
           <t>W0052-3</t>
-        </is>
-      </c>
-      <c r="B202" s="3" t="inlineStr">
-        <is>
-          <t>K0052</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
@@ -23003,12 +23003,12 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
+          <t>K0053</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
           <t>W0053-1</t>
-        </is>
-      </c>
-      <c r="B203" s="3" t="inlineStr">
-        <is>
-          <t>K0053</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
@@ -23115,12 +23115,12 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
+          <t>K0053</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
           <t>W0053-2</t>
-        </is>
-      </c>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>K0053</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
@@ -23227,12 +23227,12 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
+          <t>K0053</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
           <t>W0053-3</t>
-        </is>
-      </c>
-      <c r="B205" s="3" t="inlineStr">
-        <is>
-          <t>K0053</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
@@ -23339,12 +23339,12 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
+          <t>K0054</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
           <t>W0054-1</t>
-        </is>
-      </c>
-      <c r="B206" s="3" t="inlineStr">
-        <is>
-          <t>K0054</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
@@ -23451,12 +23451,12 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
+          <t>K0054</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
           <t>W0054-2</t>
-        </is>
-      </c>
-      <c r="B207" s="3" t="inlineStr">
-        <is>
-          <t>K0054</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
@@ -23563,14 +23563,14 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
+          <t>K0054</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
           <t>W0054-3</t>
         </is>
       </c>
-      <c r="B208" s="3" t="inlineStr">
-        <is>
-          <t>K0054</t>
-        </is>
-      </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
           <t>Hana Maulana</t>
@@ -23603,7 +23603,7 @@
       </c>
       <c r="I208" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J208" s="3" t="inlineStr">
@@ -23675,12 +23675,12 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
+          <t>K0054</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
           <t>W0054-4</t>
-        </is>
-      </c>
-      <c r="B209" s="3" t="inlineStr">
-        <is>
-          <t>K0054</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
@@ -23787,12 +23787,12 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
+          <t>K0055</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
           <t>W0055-1</t>
-        </is>
-      </c>
-      <c r="B210" s="3" t="inlineStr">
-        <is>
-          <t>K0055</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
@@ -23899,12 +23899,12 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
+          <t>K0055</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
           <t>W0055-2</t>
-        </is>
-      </c>
-      <c r="B211" s="3" t="inlineStr">
-        <is>
-          <t>K0055</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
@@ -24011,14 +24011,14 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
+          <t>K0055</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
           <t>W0055-3</t>
         </is>
       </c>
-      <c r="B212" s="3" t="inlineStr">
-        <is>
-          <t>K0055</t>
-        </is>
-      </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
           <t>Okta Permana</t>
@@ -24051,7 +24051,7 @@
       </c>
       <c r="I212" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J212" s="3" t="inlineStr">
@@ -24123,12 +24123,12 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
+          <t>K0056</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
           <t>W0056-1</t>
-        </is>
-      </c>
-      <c r="B213" s="3" t="inlineStr">
-        <is>
-          <t>K0056</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
@@ -24235,12 +24235,12 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
+          <t>K0056</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
           <t>W0056-2</t>
-        </is>
-      </c>
-      <c r="B214" s="3" t="inlineStr">
-        <is>
-          <t>K0056</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
@@ -24347,12 +24347,12 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
+          <t>K0056</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
           <t>W0056-3</t>
-        </is>
-      </c>
-      <c r="B215" s="3" t="inlineStr">
-        <is>
-          <t>K0056</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
@@ -24459,14 +24459,14 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
+          <t>K0056</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
           <t>W0056-4</t>
         </is>
       </c>
-      <c r="B216" s="3" t="inlineStr">
-        <is>
-          <t>K0056</t>
-        </is>
-      </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
           <t>Wisnu Firmansyah</t>
@@ -24499,7 +24499,7 @@
       </c>
       <c r="I216" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J216" s="3" t="inlineStr">
@@ -24571,12 +24571,12 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
+          <t>K0056</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
           <t>W0056-5</t>
-        </is>
-      </c>
-      <c r="B217" s="3" t="inlineStr">
-        <is>
-          <t>K0056</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
@@ -24683,12 +24683,12 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
+          <t>K0057</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
           <t>W0057-1</t>
-        </is>
-      </c>
-      <c r="B218" s="3" t="inlineStr">
-        <is>
-          <t>K0057</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
@@ -24795,12 +24795,12 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
+          <t>K0057</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
           <t>W0057-2</t>
-        </is>
-      </c>
-      <c r="B219" s="3" t="inlineStr">
-        <is>
-          <t>K0057</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
@@ -24907,12 +24907,12 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
+          <t>K0057</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
           <t>W0057-3</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="inlineStr">
-        <is>
-          <t>K0057</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
@@ -25019,12 +25019,12 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
+          <t>K0057</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
           <t>W0057-4</t>
-        </is>
-      </c>
-      <c r="B221" s="3" t="inlineStr">
-        <is>
-          <t>K0057</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
@@ -25131,12 +25131,12 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
+          <t>K0057</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
           <t>W0057-5</t>
-        </is>
-      </c>
-      <c r="B222" s="3" t="inlineStr">
-        <is>
-          <t>K0057</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
@@ -25243,12 +25243,12 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
+          <t>K0058</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
           <t>W0058-1</t>
-        </is>
-      </c>
-      <c r="B223" s="3" t="inlineStr">
-        <is>
-          <t>K0058</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
@@ -25355,12 +25355,12 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
+          <t>K0058</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
           <t>W0058-2</t>
-        </is>
-      </c>
-      <c r="B224" s="3" t="inlineStr">
-        <is>
-          <t>K0058</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
@@ -25467,12 +25467,12 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
+          <t>K0058</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
           <t>W0058-3</t>
-        </is>
-      </c>
-      <c r="B225" s="3" t="inlineStr">
-        <is>
-          <t>K0058</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
@@ -25579,12 +25579,12 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
+          <t>K0058</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
           <t>W0058-4</t>
-        </is>
-      </c>
-      <c r="B226" s="3" t="inlineStr">
-        <is>
-          <t>K0058</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
@@ -25691,12 +25691,12 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
+          <t>K0059</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
           <t>W0059-1</t>
-        </is>
-      </c>
-      <c r="B227" s="3" t="inlineStr">
-        <is>
-          <t>K0059</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
@@ -25803,12 +25803,12 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
+          <t>K0059</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
           <t>W0059-2</t>
-        </is>
-      </c>
-      <c r="B228" s="3" t="inlineStr">
-        <is>
-          <t>K0059</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
@@ -25915,12 +25915,12 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
+          <t>K0059</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
           <t>W0059-3</t>
-        </is>
-      </c>
-      <c r="B229" s="3" t="inlineStr">
-        <is>
-          <t>K0059</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
@@ -26027,12 +26027,12 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
+          <t>K0059</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
           <t>W0059-4</t>
-        </is>
-      </c>
-      <c r="B230" s="3" t="inlineStr">
-        <is>
-          <t>K0059</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
@@ -26139,12 +26139,12 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
+          <t>K0060</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
           <t>W0060-1</t>
-        </is>
-      </c>
-      <c r="B231" s="3" t="inlineStr">
-        <is>
-          <t>K0060</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
@@ -26251,12 +26251,12 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
+          <t>K0060</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
           <t>W0060-2</t>
-        </is>
-      </c>
-      <c r="B232" s="3" t="inlineStr">
-        <is>
-          <t>K0060</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
@@ -26363,14 +26363,14 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
+          <t>K0060</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
           <t>W0060-3</t>
         </is>
       </c>
-      <c r="B233" s="3" t="inlineStr">
-        <is>
-          <t>K0060</t>
-        </is>
-      </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
           <t>Mahesa Wijaya</t>
@@ -26403,7 +26403,7 @@
       </c>
       <c r="I233" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J233" s="3" t="inlineStr">
@@ -26475,14 +26475,14 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
+          <t>K0060</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
           <t>W0060-4</t>
         </is>
       </c>
-      <c r="B234" s="3" t="inlineStr">
-        <is>
-          <t>K0060</t>
-        </is>
-      </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
           <t>Teguh Wijaya</t>
@@ -26515,7 +26515,7 @@
       </c>
       <c r="I234" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J234" s="3" t="inlineStr">
@@ -26587,12 +26587,12 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
+          <t>K0061</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
           <t>W0061-1</t>
-        </is>
-      </c>
-      <c r="B235" s="3" t="inlineStr">
-        <is>
-          <t>K0061</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
@@ -26699,12 +26699,12 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
+          <t>K0061</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
           <t>W0061-2</t>
-        </is>
-      </c>
-      <c r="B236" s="3" t="inlineStr">
-        <is>
-          <t>K0061</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
@@ -26811,12 +26811,12 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
+          <t>K0061</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
           <t>W0061-3</t>
-        </is>
-      </c>
-      <c r="B237" s="3" t="inlineStr">
-        <is>
-          <t>K0061</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
@@ -26923,12 +26923,12 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
+          <t>K0062</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
           <t>W0062-1</t>
-        </is>
-      </c>
-      <c r="B238" s="3" t="inlineStr">
-        <is>
-          <t>K0062</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
@@ -27035,12 +27035,12 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
+          <t>K0062</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
           <t>W0062-2</t>
-        </is>
-      </c>
-      <c r="B239" s="3" t="inlineStr">
-        <is>
-          <t>K0062</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
@@ -27147,12 +27147,12 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
+          <t>K0062</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
           <t>W0062-3</t>
-        </is>
-      </c>
-      <c r="B240" s="3" t="inlineStr">
-        <is>
-          <t>K0062</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
@@ -27259,12 +27259,12 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
+          <t>K0062</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
           <t>W0062-4</t>
-        </is>
-      </c>
-      <c r="B241" s="3" t="inlineStr">
-        <is>
-          <t>K0062</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
@@ -27371,14 +27371,14 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
+          <t>K0062</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
           <t>W0062-5</t>
         </is>
       </c>
-      <c r="B242" s="3" t="inlineStr">
-        <is>
-          <t>K0062</t>
-        </is>
-      </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
           <t>Keisha Wijaya</t>
@@ -27411,7 +27411,7 @@
       </c>
       <c r="I242" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J242" s="3" t="inlineStr">
@@ -27483,12 +27483,12 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
+          <t>K0063</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
           <t>W0063-1</t>
-        </is>
-      </c>
-      <c r="B243" s="3" t="inlineStr">
-        <is>
-          <t>K0063</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
@@ -27595,12 +27595,12 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
+          <t>K0063</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
           <t>W0063-2</t>
-        </is>
-      </c>
-      <c r="B244" s="3" t="inlineStr">
-        <is>
-          <t>K0063</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
@@ -27707,12 +27707,12 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
+          <t>K0063</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
           <t>W0063-3</t>
-        </is>
-      </c>
-      <c r="B245" s="3" t="inlineStr">
-        <is>
-          <t>K0063</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
@@ -27819,12 +27819,12 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
+          <t>K0063</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
           <t>W0063-4</t>
-        </is>
-      </c>
-      <c r="B246" s="3" t="inlineStr">
-        <is>
-          <t>K0063</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
@@ -27931,12 +27931,12 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
+          <t>K0064</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
           <t>W0064-1</t>
-        </is>
-      </c>
-      <c r="B247" s="3" t="inlineStr">
-        <is>
-          <t>K0064</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
@@ -28043,12 +28043,12 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
+          <t>K0064</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
           <t>W0064-2</t>
-        </is>
-      </c>
-      <c r="B248" s="3" t="inlineStr">
-        <is>
-          <t>K0064</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
@@ -28155,12 +28155,12 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
+          <t>K0064</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
           <t>W0064-3</t>
-        </is>
-      </c>
-      <c r="B249" s="3" t="inlineStr">
-        <is>
-          <t>K0064</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
@@ -28267,12 +28267,12 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
+          <t>K0065</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
           <t>W0065-1</t>
-        </is>
-      </c>
-      <c r="B250" s="3" t="inlineStr">
-        <is>
-          <t>K0065</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
@@ -28379,12 +28379,12 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
+          <t>K0065</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
           <t>W0065-2</t>
-        </is>
-      </c>
-      <c r="B251" s="3" t="inlineStr">
-        <is>
-          <t>K0065</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
@@ -28491,12 +28491,12 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
+          <t>K0065</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
           <t>W0065-3</t>
-        </is>
-      </c>
-      <c r="B252" s="3" t="inlineStr">
-        <is>
-          <t>K0065</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
@@ -28603,12 +28603,12 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
+          <t>K0066</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
           <t>W0066-1</t>
-        </is>
-      </c>
-      <c r="B253" s="3" t="inlineStr">
-        <is>
-          <t>K0066</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
@@ -28715,12 +28715,12 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
+          <t>K0066</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
           <t>W0066-2</t>
-        </is>
-      </c>
-      <c r="B254" s="3" t="inlineStr">
-        <is>
-          <t>K0066</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
@@ -28827,12 +28827,12 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
+          <t>K0066</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
           <t>W0066-3</t>
-        </is>
-      </c>
-      <c r="B255" s="3" t="inlineStr">
-        <is>
-          <t>K0066</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
@@ -28939,12 +28939,12 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
+          <t>K0066</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
           <t>W0066-4</t>
-        </is>
-      </c>
-      <c r="B256" s="3" t="inlineStr">
-        <is>
-          <t>K0066</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
@@ -29051,12 +29051,12 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
+          <t>K0067</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
           <t>W0067-1</t>
-        </is>
-      </c>
-      <c r="B257" s="3" t="inlineStr">
-        <is>
-          <t>K0067</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
@@ -29163,12 +29163,12 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
+          <t>K0067</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
           <t>W0067-2</t>
-        </is>
-      </c>
-      <c r="B258" s="3" t="inlineStr">
-        <is>
-          <t>K0067</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
@@ -29275,12 +29275,12 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
+          <t>K0067</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
           <t>W0067-3</t>
-        </is>
-      </c>
-      <c r="B259" s="3" t="inlineStr">
-        <is>
-          <t>K0067</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
@@ -29387,12 +29387,12 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
+          <t>K0067</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
           <t>W0067-4</t>
-        </is>
-      </c>
-      <c r="B260" s="3" t="inlineStr">
-        <is>
-          <t>K0067</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
@@ -29499,12 +29499,12 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
+          <t>K0067</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
           <t>W0067-5</t>
-        </is>
-      </c>
-      <c r="B261" s="3" t="inlineStr">
-        <is>
-          <t>K0067</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
@@ -29611,12 +29611,12 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
+          <t>K0068</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
           <t>W0068-1</t>
-        </is>
-      </c>
-      <c r="B262" s="3" t="inlineStr">
-        <is>
-          <t>K0068</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
@@ -29723,12 +29723,12 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
+          <t>K0068</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
           <t>W0068-2</t>
-        </is>
-      </c>
-      <c r="B263" s="3" t="inlineStr">
-        <is>
-          <t>K0068</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
@@ -29835,12 +29835,12 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
+          <t>K0068</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
           <t>W0068-3</t>
-        </is>
-      </c>
-      <c r="B264" s="3" t="inlineStr">
-        <is>
-          <t>K0068</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
@@ -29947,12 +29947,12 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
+          <t>K0068</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
           <t>W0068-4</t>
-        </is>
-      </c>
-      <c r="B265" s="3" t="inlineStr">
-        <is>
-          <t>K0068</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
@@ -30059,12 +30059,12 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
+          <t>K0068</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
           <t>W0068-5</t>
-        </is>
-      </c>
-      <c r="B266" s="3" t="inlineStr">
-        <is>
-          <t>K0068</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
@@ -30171,12 +30171,12 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
+          <t>K0069</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
           <t>W0069-1</t>
-        </is>
-      </c>
-      <c r="B267" s="3" t="inlineStr">
-        <is>
-          <t>K0069</t>
         </is>
       </c>
       <c r="C267" s="3" t="inlineStr">
@@ -30283,12 +30283,12 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
+          <t>K0069</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
           <t>W0069-2</t>
-        </is>
-      </c>
-      <c r="B268" s="3" t="inlineStr">
-        <is>
-          <t>K0069</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
@@ -30395,12 +30395,12 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
+          <t>K0069</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
           <t>W0069-3</t>
-        </is>
-      </c>
-      <c r="B269" s="3" t="inlineStr">
-        <is>
-          <t>K0069</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
@@ -30507,12 +30507,12 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
+          <t>K0070</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
           <t>W0070-1</t>
-        </is>
-      </c>
-      <c r="B270" s="3" t="inlineStr">
-        <is>
-          <t>K0070</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
@@ -30619,12 +30619,12 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
+          <t>K0070</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
           <t>W0070-2</t>
-        </is>
-      </c>
-      <c r="B271" s="3" t="inlineStr">
-        <is>
-          <t>K0070</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
@@ -30731,12 +30731,12 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
+          <t>K0070</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
           <t>W0070-3</t>
-        </is>
-      </c>
-      <c r="B272" s="3" t="inlineStr">
-        <is>
-          <t>K0070</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
@@ -30843,12 +30843,12 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
+          <t>K0071</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
           <t>W0071-1</t>
-        </is>
-      </c>
-      <c r="B273" s="3" t="inlineStr">
-        <is>
-          <t>K0071</t>
         </is>
       </c>
       <c r="C273" s="3" t="inlineStr">
@@ -30955,12 +30955,12 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
+          <t>K0071</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
           <t>W0071-2</t>
-        </is>
-      </c>
-      <c r="B274" s="3" t="inlineStr">
-        <is>
-          <t>K0071</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
@@ -31067,12 +31067,12 @@
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
+          <t>K0071</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
           <t>W0071-3</t>
-        </is>
-      </c>
-      <c r="B275" s="3" t="inlineStr">
-        <is>
-          <t>K0071</t>
         </is>
       </c>
       <c r="C275" s="3" t="inlineStr">
@@ -31179,12 +31179,12 @@
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
+          <t>K0071</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
           <t>W0071-4</t>
-        </is>
-      </c>
-      <c r="B276" s="3" t="inlineStr">
-        <is>
-          <t>K0071</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
@@ -31291,12 +31291,12 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
+          <t>K0071</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
           <t>W0071-5</t>
-        </is>
-      </c>
-      <c r="B277" s="3" t="inlineStr">
-        <is>
-          <t>K0071</t>
         </is>
       </c>
       <c r="C277" s="3" t="inlineStr">
@@ -31403,12 +31403,12 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
+          <t>K0072</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
           <t>W0072-1</t>
-        </is>
-      </c>
-      <c r="B278" s="3" t="inlineStr">
-        <is>
-          <t>K0072</t>
         </is>
       </c>
       <c r="C278" s="3" t="inlineStr">
@@ -31515,12 +31515,12 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
+          <t>K0072</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
           <t>W0072-2</t>
-        </is>
-      </c>
-      <c r="B279" s="3" t="inlineStr">
-        <is>
-          <t>K0072</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
@@ -31627,12 +31627,12 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
+          <t>K0072</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
           <t>W0072-3</t>
-        </is>
-      </c>
-      <c r="B280" s="3" t="inlineStr">
-        <is>
-          <t>K0072</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
@@ -31739,14 +31739,14 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
+          <t>K0072</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
           <t>W0072-4</t>
         </is>
       </c>
-      <c r="B281" s="3" t="inlineStr">
-        <is>
-          <t>K0072</t>
-        </is>
-      </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
           <t>Satria Ramadhan</t>
@@ -31779,7 +31779,7 @@
       </c>
       <c r="I281" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J281" s="3" t="inlineStr">
@@ -31851,12 +31851,12 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
+          <t>K0073</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
           <t>W0073-1</t>
-        </is>
-      </c>
-      <c r="B282" s="3" t="inlineStr">
-        <is>
-          <t>K0073</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
@@ -31963,12 +31963,12 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
+          <t>K0073</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
           <t>W0073-2</t>
-        </is>
-      </c>
-      <c r="B283" s="3" t="inlineStr">
-        <is>
-          <t>K0073</t>
         </is>
       </c>
       <c r="C283" s="3" t="inlineStr">
@@ -32075,12 +32075,12 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
+          <t>K0073</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
           <t>W0073-3</t>
-        </is>
-      </c>
-      <c r="B284" s="3" t="inlineStr">
-        <is>
-          <t>K0073</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
@@ -32187,12 +32187,12 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
+          <t>K0074</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
           <t>W0074-1</t>
-        </is>
-      </c>
-      <c r="B285" s="3" t="inlineStr">
-        <is>
-          <t>K0074</t>
         </is>
       </c>
       <c r="C285" s="3" t="inlineStr">
@@ -32299,12 +32299,12 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
+          <t>K0074</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
           <t>W0074-2</t>
-        </is>
-      </c>
-      <c r="B286" s="3" t="inlineStr">
-        <is>
-          <t>K0074</t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
@@ -32411,12 +32411,12 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
+          <t>K0074</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
           <t>W0074-3</t>
-        </is>
-      </c>
-      <c r="B287" s="3" t="inlineStr">
-        <is>
-          <t>K0074</t>
         </is>
       </c>
       <c r="C287" s="3" t="inlineStr">
@@ -32523,12 +32523,12 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
+          <t>K0074</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
           <t>W0074-4</t>
-        </is>
-      </c>
-      <c r="B288" s="3" t="inlineStr">
-        <is>
-          <t>K0074</t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
@@ -32635,12 +32635,12 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
+          <t>K0075</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
           <t>W0075-1</t>
-        </is>
-      </c>
-      <c r="B289" s="3" t="inlineStr">
-        <is>
-          <t>K0075</t>
         </is>
       </c>
       <c r="C289" s="3" t="inlineStr">
@@ -32747,12 +32747,12 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
+          <t>K0075</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
           <t>W0075-2</t>
-        </is>
-      </c>
-      <c r="B290" s="3" t="inlineStr">
-        <is>
-          <t>K0075</t>
         </is>
       </c>
       <c r="C290" s="3" t="inlineStr">
@@ -32859,12 +32859,12 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
+          <t>K0075</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="inlineStr">
+        <is>
           <t>W0075-3</t>
-        </is>
-      </c>
-      <c r="B291" s="3" t="inlineStr">
-        <is>
-          <t>K0075</t>
         </is>
       </c>
       <c r="C291" s="3" t="inlineStr">
@@ -32971,12 +32971,12 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
+          <t>K0075</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
           <t>W0075-4</t>
-        </is>
-      </c>
-      <c r="B292" s="3" t="inlineStr">
-        <is>
-          <t>K0075</t>
         </is>
       </c>
       <c r="C292" s="3" t="inlineStr">
@@ -33083,12 +33083,12 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
+          <t>K0076</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
           <t>W0076-1</t>
-        </is>
-      </c>
-      <c r="B293" s="3" t="inlineStr">
-        <is>
-          <t>K0076</t>
         </is>
       </c>
       <c r="C293" s="3" t="inlineStr">
@@ -33195,12 +33195,12 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
+          <t>K0076</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
           <t>W0076-2</t>
-        </is>
-      </c>
-      <c r="B294" s="3" t="inlineStr">
-        <is>
-          <t>K0076</t>
         </is>
       </c>
       <c r="C294" s="3" t="inlineStr">
@@ -33307,12 +33307,12 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
+          <t>K0076</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
           <t>W0076-3</t>
-        </is>
-      </c>
-      <c r="B295" s="3" t="inlineStr">
-        <is>
-          <t>K0076</t>
         </is>
       </c>
       <c r="C295" s="3" t="inlineStr">
@@ -33419,12 +33419,12 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
+          <t>K0076</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
           <t>W0076-4</t>
-        </is>
-      </c>
-      <c r="B296" s="3" t="inlineStr">
-        <is>
-          <t>K0076</t>
         </is>
       </c>
       <c r="C296" s="3" t="inlineStr">
@@ -33531,12 +33531,12 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
+          <t>K0077</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
           <t>W0077-1</t>
-        </is>
-      </c>
-      <c r="B297" s="3" t="inlineStr">
-        <is>
-          <t>K0077</t>
         </is>
       </c>
       <c r="C297" s="3" t="inlineStr">
@@ -33643,12 +33643,12 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
+          <t>K0077</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
           <t>W0077-2</t>
-        </is>
-      </c>
-      <c r="B298" s="3" t="inlineStr">
-        <is>
-          <t>K0077</t>
         </is>
       </c>
       <c r="C298" s="3" t="inlineStr">
@@ -33755,12 +33755,12 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
+          <t>K0077</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
           <t>W0077-3</t>
-        </is>
-      </c>
-      <c r="B299" s="3" t="inlineStr">
-        <is>
-          <t>K0077</t>
         </is>
       </c>
       <c r="C299" s="3" t="inlineStr">
@@ -33867,12 +33867,12 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
+          <t>K0077</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
           <t>W0077-4</t>
-        </is>
-      </c>
-      <c r="B300" s="3" t="inlineStr">
-        <is>
-          <t>K0077</t>
         </is>
       </c>
       <c r="C300" s="3" t="inlineStr">
@@ -33979,12 +33979,12 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
+          <t>K0078</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
+        <is>
           <t>W0078-1</t>
-        </is>
-      </c>
-      <c r="B301" s="3" t="inlineStr">
-        <is>
-          <t>K0078</t>
         </is>
       </c>
       <c r="C301" s="3" t="inlineStr">
@@ -34091,12 +34091,12 @@
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
+          <t>K0078</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
           <t>W0078-2</t>
-        </is>
-      </c>
-      <c r="B302" s="3" t="inlineStr">
-        <is>
-          <t>K0078</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
@@ -34203,12 +34203,12 @@
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
+          <t>K0078</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="inlineStr">
+        <is>
           <t>W0078-3</t>
-        </is>
-      </c>
-      <c r="B303" s="3" t="inlineStr">
-        <is>
-          <t>K0078</t>
         </is>
       </c>
       <c r="C303" s="3" t="inlineStr">
@@ -34315,12 +34315,12 @@
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
+          <t>K0079</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
           <t>W0079-1</t>
-        </is>
-      </c>
-      <c r="B304" s="3" t="inlineStr">
-        <is>
-          <t>K0079</t>
         </is>
       </c>
       <c r="C304" s="3" t="inlineStr">
@@ -34427,12 +34427,12 @@
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
         <is>
+          <t>K0079</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
           <t>W0079-2</t>
-        </is>
-      </c>
-      <c r="B305" s="3" t="inlineStr">
-        <is>
-          <t>K0079</t>
         </is>
       </c>
       <c r="C305" s="3" t="inlineStr">
@@ -34539,12 +34539,12 @@
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
         <is>
+          <t>K0079</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
           <t>W0079-3</t>
-        </is>
-      </c>
-      <c r="B306" s="3" t="inlineStr">
-        <is>
-          <t>K0079</t>
         </is>
       </c>
       <c r="C306" s="3" t="inlineStr">
@@ -34651,14 +34651,14 @@
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
         <is>
+          <t>K0079</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
           <t>W0079-4</t>
         </is>
       </c>
-      <c r="B307" s="3" t="inlineStr">
-        <is>
-          <t>K0079</t>
-        </is>
-      </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
           <t>Cinta Gunawan</t>
@@ -34691,7 +34691,7 @@
       </c>
       <c r="I307" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J307" s="3" t="inlineStr">
@@ -34763,12 +34763,12 @@
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
+          <t>K0079</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
           <t>W0079-5</t>
-        </is>
-      </c>
-      <c r="B308" s="3" t="inlineStr">
-        <is>
-          <t>K0079</t>
         </is>
       </c>
       <c r="C308" s="3" t="inlineStr">
@@ -34875,12 +34875,12 @@
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
         <is>
+          <t>K0080</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
           <t>W0080-1</t>
-        </is>
-      </c>
-      <c r="B309" s="3" t="inlineStr">
-        <is>
-          <t>K0080</t>
         </is>
       </c>
       <c r="C309" s="3" t="inlineStr">
@@ -34987,12 +34987,12 @@
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
         <is>
+          <t>K0080</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
           <t>W0080-2</t>
-        </is>
-      </c>
-      <c r="B310" s="3" t="inlineStr">
-        <is>
-          <t>K0080</t>
         </is>
       </c>
       <c r="C310" s="3" t="inlineStr">
@@ -35099,12 +35099,12 @@
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
         <is>
+          <t>K0080</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="inlineStr">
+        <is>
           <t>W0080-3</t>
-        </is>
-      </c>
-      <c r="B311" s="3" t="inlineStr">
-        <is>
-          <t>K0080</t>
         </is>
       </c>
       <c r="C311" s="3" t="inlineStr">
@@ -35211,12 +35211,12 @@
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
         <is>
+          <t>K0081</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
           <t>W0081-1</t>
-        </is>
-      </c>
-      <c r="B312" s="3" t="inlineStr">
-        <is>
-          <t>K0081</t>
         </is>
       </c>
       <c r="C312" s="3" t="inlineStr">
@@ -35323,12 +35323,12 @@
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
         <is>
+          <t>K0081</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="inlineStr">
+        <is>
           <t>W0081-2</t>
-        </is>
-      </c>
-      <c r="B313" s="3" t="inlineStr">
-        <is>
-          <t>K0081</t>
         </is>
       </c>
       <c r="C313" s="3" t="inlineStr">
@@ -35435,12 +35435,12 @@
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
         <is>
+          <t>K0081</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
           <t>W0081-3</t>
-        </is>
-      </c>
-      <c r="B314" s="3" t="inlineStr">
-        <is>
-          <t>K0081</t>
         </is>
       </c>
       <c r="C314" s="3" t="inlineStr">
@@ -35547,12 +35547,12 @@
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
         <is>
+          <t>K0082</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
           <t>W0082-1</t>
-        </is>
-      </c>
-      <c r="B315" s="3" t="inlineStr">
-        <is>
-          <t>K0082</t>
         </is>
       </c>
       <c r="C315" s="3" t="inlineStr">
@@ -35659,12 +35659,12 @@
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
         <is>
+          <t>K0082</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
           <t>W0082-2</t>
-        </is>
-      </c>
-      <c r="B316" s="3" t="inlineStr">
-        <is>
-          <t>K0082</t>
         </is>
       </c>
       <c r="C316" s="3" t="inlineStr">
@@ -35771,12 +35771,12 @@
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
         <is>
+          <t>K0082</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
           <t>W0082-3</t>
-        </is>
-      </c>
-      <c r="B317" s="3" t="inlineStr">
-        <is>
-          <t>K0082</t>
         </is>
       </c>
       <c r="C317" s="3" t="inlineStr">
@@ -35883,12 +35883,12 @@
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
         <is>
+          <t>K0083</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
           <t>W0083-1</t>
-        </is>
-      </c>
-      <c r="B318" s="3" t="inlineStr">
-        <is>
-          <t>K0083</t>
         </is>
       </c>
       <c r="C318" s="3" t="inlineStr">
@@ -35995,12 +35995,12 @@
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
         <is>
+          <t>K0083</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="inlineStr">
+        <is>
           <t>W0083-2</t>
-        </is>
-      </c>
-      <c r="B319" s="3" t="inlineStr">
-        <is>
-          <t>K0083</t>
         </is>
       </c>
       <c r="C319" s="3" t="inlineStr">
@@ -36107,12 +36107,12 @@
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
         <is>
+          <t>K0083</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="inlineStr">
+        <is>
           <t>W0083-3</t>
-        </is>
-      </c>
-      <c r="B320" s="3" t="inlineStr">
-        <is>
-          <t>K0083</t>
         </is>
       </c>
       <c r="C320" s="3" t="inlineStr">
@@ -36219,12 +36219,12 @@
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
         <is>
+          <t>K0084</t>
+        </is>
+      </c>
+      <c r="B321" s="3" t="inlineStr">
+        <is>
           <t>W0084-1</t>
-        </is>
-      </c>
-      <c r="B321" s="3" t="inlineStr">
-        <is>
-          <t>K0084</t>
         </is>
       </c>
       <c r="C321" s="3" t="inlineStr">
@@ -36331,12 +36331,12 @@
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
         <is>
+          <t>K0084</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="inlineStr">
+        <is>
           <t>W0084-2</t>
-        </is>
-      </c>
-      <c r="B322" s="3" t="inlineStr">
-        <is>
-          <t>K0084</t>
         </is>
       </c>
       <c r="C322" s="3" t="inlineStr">
@@ -36443,12 +36443,12 @@
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
         <is>
+          <t>K0084</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
           <t>W0084-3</t>
-        </is>
-      </c>
-      <c r="B323" s="3" t="inlineStr">
-        <is>
-          <t>K0084</t>
         </is>
       </c>
       <c r="C323" s="3" t="inlineStr">
@@ -36555,12 +36555,12 @@
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
         <is>
+          <t>K0084</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
           <t>W0084-4</t>
-        </is>
-      </c>
-      <c r="B324" s="3" t="inlineStr">
-        <is>
-          <t>K0084</t>
         </is>
       </c>
       <c r="C324" s="3" t="inlineStr">
@@ -36667,14 +36667,14 @@
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
         <is>
+          <t>K0084</t>
+        </is>
+      </c>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
           <t>W0084-5</t>
         </is>
       </c>
-      <c r="B325" s="3" t="inlineStr">
-        <is>
-          <t>K0084</t>
-        </is>
-      </c>
       <c r="C325" s="3" t="inlineStr">
         <is>
           <t>Jefri Setiawan</t>
@@ -36707,7 +36707,7 @@
       </c>
       <c r="I325" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J325" s="3" t="inlineStr">
@@ -36779,12 +36779,12 @@
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
         <is>
+          <t>K0085</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="inlineStr">
+        <is>
           <t>W0085-1</t>
-        </is>
-      </c>
-      <c r="B326" s="3" t="inlineStr">
-        <is>
-          <t>K0085</t>
         </is>
       </c>
       <c r="C326" s="3" t="inlineStr">
@@ -36891,12 +36891,12 @@
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
         <is>
+          <t>K0085</t>
+        </is>
+      </c>
+      <c r="B327" s="3" t="inlineStr">
+        <is>
           <t>W0085-2</t>
-        </is>
-      </c>
-      <c r="B327" s="3" t="inlineStr">
-        <is>
-          <t>K0085</t>
         </is>
       </c>
       <c r="C327" s="3" t="inlineStr">
@@ -37003,14 +37003,14 @@
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
         <is>
+          <t>K0085</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="inlineStr">
+        <is>
           <t>W0085-3</t>
         </is>
       </c>
-      <c r="B328" s="3" t="inlineStr">
-        <is>
-          <t>K0085</t>
-        </is>
-      </c>
       <c r="C328" s="3" t="inlineStr">
         <is>
           <t>Rani Firmansyah</t>
@@ -37043,7 +37043,7 @@
       </c>
       <c r="I328" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J328" s="3" t="inlineStr">
@@ -37115,12 +37115,12 @@
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
         <is>
+          <t>K0085</t>
+        </is>
+      </c>
+      <c r="B329" s="3" t="inlineStr">
+        <is>
           <t>W0085-4</t>
-        </is>
-      </c>
-      <c r="B329" s="3" t="inlineStr">
-        <is>
-          <t>K0085</t>
         </is>
       </c>
       <c r="C329" s="3" t="inlineStr">
@@ -37227,14 +37227,14 @@
     <row r="330">
       <c r="A330" s="3" t="inlineStr">
         <is>
+          <t>K0085</t>
+        </is>
+      </c>
+      <c r="B330" s="3" t="inlineStr">
+        <is>
           <t>W0085-5</t>
         </is>
       </c>
-      <c r="B330" s="3" t="inlineStr">
-        <is>
-          <t>K0085</t>
-        </is>
-      </c>
       <c r="C330" s="3" t="inlineStr">
         <is>
           <t>Adit Firmansyah</t>
@@ -37267,7 +37267,7 @@
       </c>
       <c r="I330" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J330" s="3" t="inlineStr">
@@ -37339,12 +37339,12 @@
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
         <is>
+          <t>K0086</t>
+        </is>
+      </c>
+      <c r="B331" s="3" t="inlineStr">
+        <is>
           <t>W0086-1</t>
-        </is>
-      </c>
-      <c r="B331" s="3" t="inlineStr">
-        <is>
-          <t>K0086</t>
         </is>
       </c>
       <c r="C331" s="3" t="inlineStr">
@@ -37451,12 +37451,12 @@
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
         <is>
+          <t>K0086</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="inlineStr">
+        <is>
           <t>W0086-2</t>
-        </is>
-      </c>
-      <c r="B332" s="3" t="inlineStr">
-        <is>
-          <t>K0086</t>
         </is>
       </c>
       <c r="C332" s="3" t="inlineStr">
@@ -37563,14 +37563,14 @@
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
         <is>
+          <t>K0086</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="inlineStr">
+        <is>
           <t>W0086-3</t>
         </is>
       </c>
-      <c r="B333" s="3" t="inlineStr">
-        <is>
-          <t>K0086</t>
-        </is>
-      </c>
       <c r="C333" s="3" t="inlineStr">
         <is>
           <t>Ulfa Firmansyah</t>
@@ -37603,7 +37603,7 @@
       </c>
       <c r="I333" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J333" s="3" t="inlineStr">
@@ -37675,12 +37675,12 @@
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
         <is>
+          <t>K0087</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="inlineStr">
+        <is>
           <t>W0087-1</t>
-        </is>
-      </c>
-      <c r="B334" s="3" t="inlineStr">
-        <is>
-          <t>K0087</t>
         </is>
       </c>
       <c r="C334" s="3" t="inlineStr">
@@ -37787,12 +37787,12 @@
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
         <is>
+          <t>K0087</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
           <t>W0087-2</t>
-        </is>
-      </c>
-      <c r="B335" s="3" t="inlineStr">
-        <is>
-          <t>K0087</t>
         </is>
       </c>
       <c r="C335" s="3" t="inlineStr">
@@ -37899,12 +37899,12 @@
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
         <is>
+          <t>K0087</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="inlineStr">
+        <is>
           <t>W0087-3</t>
-        </is>
-      </c>
-      <c r="B336" s="3" t="inlineStr">
-        <is>
-          <t>K0087</t>
         </is>
       </c>
       <c r="C336" s="3" t="inlineStr">
@@ -38011,12 +38011,12 @@
     <row r="337">
       <c r="A337" s="3" t="inlineStr">
         <is>
+          <t>K0087</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="inlineStr">
+        <is>
           <t>W0087-4</t>
-        </is>
-      </c>
-      <c r="B337" s="3" t="inlineStr">
-        <is>
-          <t>K0087</t>
         </is>
       </c>
       <c r="C337" s="3" t="inlineStr">
@@ -38123,12 +38123,12 @@
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
         <is>
+          <t>K0087</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
           <t>W0087-5</t>
-        </is>
-      </c>
-      <c r="B338" s="3" t="inlineStr">
-        <is>
-          <t>K0087</t>
         </is>
       </c>
       <c r="C338" s="3" t="inlineStr">
@@ -38235,12 +38235,12 @@
     <row r="339">
       <c r="A339" s="3" t="inlineStr">
         <is>
+          <t>K0088</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
           <t>W0088-1</t>
-        </is>
-      </c>
-      <c r="B339" s="3" t="inlineStr">
-        <is>
-          <t>K0088</t>
         </is>
       </c>
       <c r="C339" s="3" t="inlineStr">
@@ -38347,12 +38347,12 @@
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
         <is>
+          <t>K0088</t>
+        </is>
+      </c>
+      <c r="B340" s="3" t="inlineStr">
+        <is>
           <t>W0088-2</t>
-        </is>
-      </c>
-      <c r="B340" s="3" t="inlineStr">
-        <is>
-          <t>K0088</t>
         </is>
       </c>
       <c r="C340" s="3" t="inlineStr">
@@ -38459,12 +38459,12 @@
     <row r="341">
       <c r="A341" s="3" t="inlineStr">
         <is>
+          <t>K0088</t>
+        </is>
+      </c>
+      <c r="B341" s="3" t="inlineStr">
+        <is>
           <t>W0088-3</t>
-        </is>
-      </c>
-      <c r="B341" s="3" t="inlineStr">
-        <is>
-          <t>K0088</t>
         </is>
       </c>
       <c r="C341" s="3" t="inlineStr">
@@ -38571,12 +38571,12 @@
     <row r="342">
       <c r="A342" s="3" t="inlineStr">
         <is>
+          <t>K0088</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
+        <is>
           <t>W0088-4</t>
-        </is>
-      </c>
-      <c r="B342" s="3" t="inlineStr">
-        <is>
-          <t>K0088</t>
         </is>
       </c>
       <c r="C342" s="3" t="inlineStr">
@@ -38683,12 +38683,12 @@
     <row r="343">
       <c r="A343" s="3" t="inlineStr">
         <is>
+          <t>K0089</t>
+        </is>
+      </c>
+      <c r="B343" s="3" t="inlineStr">
+        <is>
           <t>W0089-1</t>
-        </is>
-      </c>
-      <c r="B343" s="3" t="inlineStr">
-        <is>
-          <t>K0089</t>
         </is>
       </c>
       <c r="C343" s="3" t="inlineStr">
@@ -38795,12 +38795,12 @@
     <row r="344">
       <c r="A344" s="3" t="inlineStr">
         <is>
+          <t>K0089</t>
+        </is>
+      </c>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
           <t>W0089-2</t>
-        </is>
-      </c>
-      <c r="B344" s="3" t="inlineStr">
-        <is>
-          <t>K0089</t>
         </is>
       </c>
       <c r="C344" s="3" t="inlineStr">
@@ -38907,14 +38907,14 @@
     <row r="345">
       <c r="A345" s="3" t="inlineStr">
         <is>
+          <t>K0089</t>
+        </is>
+      </c>
+      <c r="B345" s="3" t="inlineStr">
+        <is>
           <t>W0089-3</t>
         </is>
       </c>
-      <c r="B345" s="3" t="inlineStr">
-        <is>
-          <t>K0089</t>
-        </is>
-      </c>
       <c r="C345" s="3" t="inlineStr">
         <is>
           <t>Mahesa Saputra</t>
@@ -38947,7 +38947,7 @@
       </c>
       <c r="I345" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J345" s="3" t="inlineStr">
@@ -39019,12 +39019,12 @@
     <row r="346">
       <c r="A346" s="3" t="inlineStr">
         <is>
+          <t>K0089</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
           <t>W0089-4</t>
-        </is>
-      </c>
-      <c r="B346" s="3" t="inlineStr">
-        <is>
-          <t>K0089</t>
         </is>
       </c>
       <c r="C346" s="3" t="inlineStr">
@@ -39131,12 +39131,12 @@
     <row r="347">
       <c r="A347" s="3" t="inlineStr">
         <is>
+          <t>K0089</t>
+        </is>
+      </c>
+      <c r="B347" s="3" t="inlineStr">
+        <is>
           <t>W0089-5</t>
-        </is>
-      </c>
-      <c r="B347" s="3" t="inlineStr">
-        <is>
-          <t>K0089</t>
         </is>
       </c>
       <c r="C347" s="3" t="inlineStr">
@@ -39243,12 +39243,12 @@
     <row r="348">
       <c r="A348" s="3" t="inlineStr">
         <is>
+          <t>K0090</t>
+        </is>
+      </c>
+      <c r="B348" s="3" t="inlineStr">
+        <is>
           <t>W0090-1</t>
-        </is>
-      </c>
-      <c r="B348" s="3" t="inlineStr">
-        <is>
-          <t>K0090</t>
         </is>
       </c>
       <c r="C348" s="3" t="inlineStr">
@@ -39355,12 +39355,12 @@
     <row r="349">
       <c r="A349" s="3" t="inlineStr">
         <is>
+          <t>K0090</t>
+        </is>
+      </c>
+      <c r="B349" s="3" t="inlineStr">
+        <is>
           <t>W0090-2</t>
-        </is>
-      </c>
-      <c r="B349" s="3" t="inlineStr">
-        <is>
-          <t>K0090</t>
         </is>
       </c>
       <c r="C349" s="3" t="inlineStr">
@@ -39467,12 +39467,12 @@
     <row r="350">
       <c r="A350" s="3" t="inlineStr">
         <is>
+          <t>K0090</t>
+        </is>
+      </c>
+      <c r="B350" s="3" t="inlineStr">
+        <is>
           <t>W0090-3</t>
-        </is>
-      </c>
-      <c r="B350" s="3" t="inlineStr">
-        <is>
-          <t>K0090</t>
         </is>
       </c>
       <c r="C350" s="3" t="inlineStr">
@@ -39579,12 +39579,12 @@
     <row r="351">
       <c r="A351" s="3" t="inlineStr">
         <is>
+          <t>K0091</t>
+        </is>
+      </c>
+      <c r="B351" s="3" t="inlineStr">
+        <is>
           <t>W0091-1</t>
-        </is>
-      </c>
-      <c r="B351" s="3" t="inlineStr">
-        <is>
-          <t>K0091</t>
         </is>
       </c>
       <c r="C351" s="3" t="inlineStr">
@@ -39691,12 +39691,12 @@
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
         <is>
+          <t>K0091</t>
+        </is>
+      </c>
+      <c r="B352" s="3" t="inlineStr">
+        <is>
           <t>W0091-2</t>
-        </is>
-      </c>
-      <c r="B352" s="3" t="inlineStr">
-        <is>
-          <t>K0091</t>
         </is>
       </c>
       <c r="C352" s="3" t="inlineStr">
@@ -39803,12 +39803,12 @@
     <row r="353">
       <c r="A353" s="3" t="inlineStr">
         <is>
+          <t>K0091</t>
+        </is>
+      </c>
+      <c r="B353" s="3" t="inlineStr">
+        <is>
           <t>W0091-3</t>
-        </is>
-      </c>
-      <c r="B353" s="3" t="inlineStr">
-        <is>
-          <t>K0091</t>
         </is>
       </c>
       <c r="C353" s="3" t="inlineStr">
@@ -39915,12 +39915,12 @@
     <row r="354">
       <c r="A354" s="3" t="inlineStr">
         <is>
+          <t>K0091</t>
+        </is>
+      </c>
+      <c r="B354" s="3" t="inlineStr">
+        <is>
           <t>W0091-4</t>
-        </is>
-      </c>
-      <c r="B354" s="3" t="inlineStr">
-        <is>
-          <t>K0091</t>
         </is>
       </c>
       <c r="C354" s="3" t="inlineStr">
@@ -40027,12 +40027,12 @@
     <row r="355">
       <c r="A355" s="3" t="inlineStr">
         <is>
+          <t>K0092</t>
+        </is>
+      </c>
+      <c r="B355" s="3" t="inlineStr">
+        <is>
           <t>W0092-1</t>
-        </is>
-      </c>
-      <c r="B355" s="3" t="inlineStr">
-        <is>
-          <t>K0092</t>
         </is>
       </c>
       <c r="C355" s="3" t="inlineStr">
@@ -40139,12 +40139,12 @@
     <row r="356">
       <c r="A356" s="3" t="inlineStr">
         <is>
+          <t>K0092</t>
+        </is>
+      </c>
+      <c r="B356" s="3" t="inlineStr">
+        <is>
           <t>W0092-2</t>
-        </is>
-      </c>
-      <c r="B356" s="3" t="inlineStr">
-        <is>
-          <t>K0092</t>
         </is>
       </c>
       <c r="C356" s="3" t="inlineStr">
@@ -40251,14 +40251,14 @@
     <row r="357">
       <c r="A357" s="3" t="inlineStr">
         <is>
+          <t>K0092</t>
+        </is>
+      </c>
+      <c r="B357" s="3" t="inlineStr">
+        <is>
           <t>W0092-3</t>
         </is>
       </c>
-      <c r="B357" s="3" t="inlineStr">
-        <is>
-          <t>K0092</t>
-        </is>
-      </c>
       <c r="C357" s="3" t="inlineStr">
         <is>
           <t>Olivia Setiawan</t>
@@ -40291,7 +40291,7 @@
       </c>
       <c r="I357" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J357" s="3" t="inlineStr">
@@ -40363,12 +40363,12 @@
     <row r="358">
       <c r="A358" s="3" t="inlineStr">
         <is>
+          <t>K0093</t>
+        </is>
+      </c>
+      <c r="B358" s="3" t="inlineStr">
+        <is>
           <t>W0093-1</t>
-        </is>
-      </c>
-      <c r="B358" s="3" t="inlineStr">
-        <is>
-          <t>K0093</t>
         </is>
       </c>
       <c r="C358" s="3" t="inlineStr">
@@ -40475,12 +40475,12 @@
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
         <is>
+          <t>K0093</t>
+        </is>
+      </c>
+      <c r="B359" s="3" t="inlineStr">
+        <is>
           <t>W0093-2</t>
-        </is>
-      </c>
-      <c r="B359" s="3" t="inlineStr">
-        <is>
-          <t>K0093</t>
         </is>
       </c>
       <c r="C359" s="3" t="inlineStr">
@@ -40587,12 +40587,12 @@
     <row r="360">
       <c r="A360" s="3" t="inlineStr">
         <is>
+          <t>K0093</t>
+        </is>
+      </c>
+      <c r="B360" s="3" t="inlineStr">
+        <is>
           <t>W0093-3</t>
-        </is>
-      </c>
-      <c r="B360" s="3" t="inlineStr">
-        <is>
-          <t>K0093</t>
         </is>
       </c>
       <c r="C360" s="3" t="inlineStr">
@@ -40699,12 +40699,12 @@
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
         <is>
+          <t>K0093</t>
+        </is>
+      </c>
+      <c r="B361" s="3" t="inlineStr">
+        <is>
           <t>W0093-4</t>
-        </is>
-      </c>
-      <c r="B361" s="3" t="inlineStr">
-        <is>
-          <t>K0093</t>
         </is>
       </c>
       <c r="C361" s="3" t="inlineStr">
@@ -40811,12 +40811,12 @@
     <row r="362">
       <c r="A362" s="3" t="inlineStr">
         <is>
+          <t>K0094</t>
+        </is>
+      </c>
+      <c r="B362" s="3" t="inlineStr">
+        <is>
           <t>W0094-1</t>
-        </is>
-      </c>
-      <c r="B362" s="3" t="inlineStr">
-        <is>
-          <t>K0094</t>
         </is>
       </c>
       <c r="C362" s="3" t="inlineStr">
@@ -40923,12 +40923,12 @@
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
         <is>
+          <t>K0094</t>
+        </is>
+      </c>
+      <c r="B363" s="3" t="inlineStr">
+        <is>
           <t>W0094-2</t>
-        </is>
-      </c>
-      <c r="B363" s="3" t="inlineStr">
-        <is>
-          <t>K0094</t>
         </is>
       </c>
       <c r="C363" s="3" t="inlineStr">
@@ -41035,14 +41035,14 @@
     <row r="364">
       <c r="A364" s="3" t="inlineStr">
         <is>
+          <t>K0094</t>
+        </is>
+      </c>
+      <c r="B364" s="3" t="inlineStr">
+        <is>
           <t>W0094-3</t>
         </is>
       </c>
-      <c r="B364" s="3" t="inlineStr">
-        <is>
-          <t>K0094</t>
-        </is>
-      </c>
       <c r="C364" s="3" t="inlineStr">
         <is>
           <t>Cahyo Susanto</t>
@@ -41075,7 +41075,7 @@
       </c>
       <c r="I364" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J364" s="3" t="inlineStr">
@@ -41147,12 +41147,12 @@
     <row r="365">
       <c r="A365" s="3" t="inlineStr">
         <is>
+          <t>K0094</t>
+        </is>
+      </c>
+      <c r="B365" s="3" t="inlineStr">
+        <is>
           <t>W0094-4</t>
-        </is>
-      </c>
-      <c r="B365" s="3" t="inlineStr">
-        <is>
-          <t>K0094</t>
         </is>
       </c>
       <c r="C365" s="3" t="inlineStr">
@@ -41259,12 +41259,12 @@
     <row r="366">
       <c r="A366" s="3" t="inlineStr">
         <is>
+          <t>K0094</t>
+        </is>
+      </c>
+      <c r="B366" s="3" t="inlineStr">
+        <is>
           <t>W0094-5</t>
-        </is>
-      </c>
-      <c r="B366" s="3" t="inlineStr">
-        <is>
-          <t>K0094</t>
         </is>
       </c>
       <c r="C366" s="3" t="inlineStr">
@@ -41371,12 +41371,12 @@
     <row r="367">
       <c r="A367" s="3" t="inlineStr">
         <is>
+          <t>K0095</t>
+        </is>
+      </c>
+      <c r="B367" s="3" t="inlineStr">
+        <is>
           <t>W0095-1</t>
-        </is>
-      </c>
-      <c r="B367" s="3" t="inlineStr">
-        <is>
-          <t>K0095</t>
         </is>
       </c>
       <c r="C367" s="3" t="inlineStr">
@@ -41483,12 +41483,12 @@
     <row r="368">
       <c r="A368" s="3" t="inlineStr">
         <is>
+          <t>K0095</t>
+        </is>
+      </c>
+      <c r="B368" s="3" t="inlineStr">
+        <is>
           <t>W0095-2</t>
-        </is>
-      </c>
-      <c r="B368" s="3" t="inlineStr">
-        <is>
-          <t>K0095</t>
         </is>
       </c>
       <c r="C368" s="3" t="inlineStr">
@@ -41595,12 +41595,12 @@
     <row r="369">
       <c r="A369" s="3" t="inlineStr">
         <is>
+          <t>K0095</t>
+        </is>
+      </c>
+      <c r="B369" s="3" t="inlineStr">
+        <is>
           <t>W0095-3</t>
-        </is>
-      </c>
-      <c r="B369" s="3" t="inlineStr">
-        <is>
-          <t>K0095</t>
         </is>
       </c>
       <c r="C369" s="3" t="inlineStr">
@@ -41707,12 +41707,12 @@
     <row r="370">
       <c r="A370" s="3" t="inlineStr">
         <is>
+          <t>K0096</t>
+        </is>
+      </c>
+      <c r="B370" s="3" t="inlineStr">
+        <is>
           <t>W0096-1</t>
-        </is>
-      </c>
-      <c r="B370" s="3" t="inlineStr">
-        <is>
-          <t>K0096</t>
         </is>
       </c>
       <c r="C370" s="3" t="inlineStr">
@@ -41819,12 +41819,12 @@
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
         <is>
+          <t>K0096</t>
+        </is>
+      </c>
+      <c r="B371" s="3" t="inlineStr">
+        <is>
           <t>W0096-2</t>
-        </is>
-      </c>
-      <c r="B371" s="3" t="inlineStr">
-        <is>
-          <t>K0096</t>
         </is>
       </c>
       <c r="C371" s="3" t="inlineStr">
@@ -41931,12 +41931,12 @@
     <row r="372">
       <c r="A372" s="3" t="inlineStr">
         <is>
+          <t>K0096</t>
+        </is>
+      </c>
+      <c r="B372" s="3" t="inlineStr">
+        <is>
           <t>W0096-3</t>
-        </is>
-      </c>
-      <c r="B372" s="3" t="inlineStr">
-        <is>
-          <t>K0096</t>
         </is>
       </c>
       <c r="C372" s="3" t="inlineStr">
@@ -42043,14 +42043,14 @@
     <row r="373">
       <c r="A373" s="3" t="inlineStr">
         <is>
+          <t>K0096</t>
+        </is>
+      </c>
+      <c r="B373" s="3" t="inlineStr">
+        <is>
           <t>W0096-4</t>
         </is>
       </c>
-      <c r="B373" s="3" t="inlineStr">
-        <is>
-          <t>K0096</t>
-        </is>
-      </c>
       <c r="C373" s="3" t="inlineStr">
         <is>
           <t>Hafiz Hidayat</t>
@@ -42083,7 +42083,7 @@
       </c>
       <c r="I373" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J373" s="3" t="inlineStr">
@@ -42155,12 +42155,12 @@
     <row r="374">
       <c r="A374" s="3" t="inlineStr">
         <is>
+          <t>K0096</t>
+        </is>
+      </c>
+      <c r="B374" s="3" t="inlineStr">
+        <is>
           <t>W0096-5</t>
-        </is>
-      </c>
-      <c r="B374" s="3" t="inlineStr">
-        <is>
-          <t>K0096</t>
         </is>
       </c>
       <c r="C374" s="3" t="inlineStr">
@@ -42267,12 +42267,12 @@
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
         <is>
+          <t>K0097</t>
+        </is>
+      </c>
+      <c r="B375" s="3" t="inlineStr">
+        <is>
           <t>W0097-1</t>
-        </is>
-      </c>
-      <c r="B375" s="3" t="inlineStr">
-        <is>
-          <t>K0097</t>
         </is>
       </c>
       <c r="C375" s="3" t="inlineStr">
@@ -42379,12 +42379,12 @@
     <row r="376">
       <c r="A376" s="3" t="inlineStr">
         <is>
+          <t>K0097</t>
+        </is>
+      </c>
+      <c r="B376" s="3" t="inlineStr">
+        <is>
           <t>W0097-2</t>
-        </is>
-      </c>
-      <c r="B376" s="3" t="inlineStr">
-        <is>
-          <t>K0097</t>
         </is>
       </c>
       <c r="C376" s="3" t="inlineStr">
@@ -42491,12 +42491,12 @@
     <row r="377">
       <c r="A377" s="3" t="inlineStr">
         <is>
+          <t>K0097</t>
+        </is>
+      </c>
+      <c r="B377" s="3" t="inlineStr">
+        <is>
           <t>W0097-3</t>
-        </is>
-      </c>
-      <c r="B377" s="3" t="inlineStr">
-        <is>
-          <t>K0097</t>
         </is>
       </c>
       <c r="C377" s="3" t="inlineStr">
@@ -42603,12 +42603,12 @@
     <row r="378">
       <c r="A378" s="3" t="inlineStr">
         <is>
+          <t>K0097</t>
+        </is>
+      </c>
+      <c r="B378" s="3" t="inlineStr">
+        <is>
           <t>W0097-4</t>
-        </is>
-      </c>
-      <c r="B378" s="3" t="inlineStr">
-        <is>
-          <t>K0097</t>
         </is>
       </c>
       <c r="C378" s="3" t="inlineStr">
@@ -42715,12 +42715,12 @@
     <row r="379">
       <c r="A379" s="3" t="inlineStr">
         <is>
+          <t>K0098</t>
+        </is>
+      </c>
+      <c r="B379" s="3" t="inlineStr">
+        <is>
           <t>W0098-1</t>
-        </is>
-      </c>
-      <c r="B379" s="3" t="inlineStr">
-        <is>
-          <t>K0098</t>
         </is>
       </c>
       <c r="C379" s="3" t="inlineStr">
@@ -42827,12 +42827,12 @@
     <row r="380">
       <c r="A380" s="3" t="inlineStr">
         <is>
+          <t>K0098</t>
+        </is>
+      </c>
+      <c r="B380" s="3" t="inlineStr">
+        <is>
           <t>W0098-2</t>
-        </is>
-      </c>
-      <c r="B380" s="3" t="inlineStr">
-        <is>
-          <t>K0098</t>
         </is>
       </c>
       <c r="C380" s="3" t="inlineStr">
@@ -42939,14 +42939,14 @@
     <row r="381">
       <c r="A381" s="3" t="inlineStr">
         <is>
+          <t>K0098</t>
+        </is>
+      </c>
+      <c r="B381" s="3" t="inlineStr">
+        <is>
           <t>W0098-3</t>
         </is>
       </c>
-      <c r="B381" s="3" t="inlineStr">
-        <is>
-          <t>K0098</t>
-        </is>
-      </c>
       <c r="C381" s="3" t="inlineStr">
         <is>
           <t>Bayu Hidayat</t>
@@ -42979,7 +42979,7 @@
       </c>
       <c r="I381" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J381" s="3" t="inlineStr">
@@ -43051,12 +43051,12 @@
     <row r="382">
       <c r="A382" s="3" t="inlineStr">
         <is>
+          <t>K0099</t>
+        </is>
+      </c>
+      <c r="B382" s="3" t="inlineStr">
+        <is>
           <t>W0099-1</t>
-        </is>
-      </c>
-      <c r="B382" s="3" t="inlineStr">
-        <is>
-          <t>K0099</t>
         </is>
       </c>
       <c r="C382" s="3" t="inlineStr">
@@ -43163,12 +43163,12 @@
     <row r="383">
       <c r="A383" s="3" t="inlineStr">
         <is>
+          <t>K0099</t>
+        </is>
+      </c>
+      <c r="B383" s="3" t="inlineStr">
+        <is>
           <t>W0099-2</t>
-        </is>
-      </c>
-      <c r="B383" s="3" t="inlineStr">
-        <is>
-          <t>K0099</t>
         </is>
       </c>
       <c r="C383" s="3" t="inlineStr">
@@ -43275,14 +43275,14 @@
     <row r="384">
       <c r="A384" s="3" t="inlineStr">
         <is>
+          <t>K0099</t>
+        </is>
+      </c>
+      <c r="B384" s="3" t="inlineStr">
+        <is>
           <t>W0099-3</t>
         </is>
       </c>
-      <c r="B384" s="3" t="inlineStr">
-        <is>
-          <t>K0099</t>
-        </is>
-      </c>
       <c r="C384" s="3" t="inlineStr">
         <is>
           <t>Olivia Permana</t>
@@ -43315,7 +43315,7 @@
       </c>
       <c r="I384" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J384" s="3" t="inlineStr">
@@ -43387,12 +43387,12 @@
     <row r="385">
       <c r="A385" s="3" t="inlineStr">
         <is>
+          <t>K0100</t>
+        </is>
+      </c>
+      <c r="B385" s="3" t="inlineStr">
+        <is>
           <t>W0100-1</t>
-        </is>
-      </c>
-      <c r="B385" s="3" t="inlineStr">
-        <is>
-          <t>K0100</t>
         </is>
       </c>
       <c r="C385" s="3" t="inlineStr">
@@ -43499,12 +43499,12 @@
     <row r="386">
       <c r="A386" s="3" t="inlineStr">
         <is>
+          <t>K0100</t>
+        </is>
+      </c>
+      <c r="B386" s="3" t="inlineStr">
+        <is>
           <t>W0100-2</t>
-        </is>
-      </c>
-      <c r="B386" s="3" t="inlineStr">
-        <is>
-          <t>K0100</t>
         </is>
       </c>
       <c r="C386" s="3" t="inlineStr">
@@ -43611,14 +43611,14 @@
     <row r="387">
       <c r="A387" s="3" t="inlineStr">
         <is>
+          <t>K0100</t>
+        </is>
+      </c>
+      <c r="B387" s="3" t="inlineStr">
+        <is>
           <t>W0100-3</t>
         </is>
       </c>
-      <c r="B387" s="3" t="inlineStr">
-        <is>
-          <t>K0100</t>
-        </is>
-      </c>
       <c r="C387" s="3" t="inlineStr">
         <is>
           <t>Dara Hidayat</t>
@@ -43651,7 +43651,7 @@
       </c>
       <c r="I387" s="3" t="inlineStr">
         <is>
-          <t>TIDAK_SEKOLAH</t>
+          <t>TIDAK_BELUM_SEKOLAH</t>
         </is>
       </c>
       <c r="J387" s="3" t="inlineStr">
